--- a/sheets/조재수대금교본/검수/초혼.xlsx
+++ b/sheets/조재수대금교본/검수/초혼.xlsx
@@ -3831,8 +3831,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲∼
-‹</t>
+          <t xml:space="preserve">仲∼</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3853,8 +3852,7 @@
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢汰
-‹</t>
+潢汰</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -3879,11 +3877,7 @@
         </is>
       </c>
       <c r="O3" s="22"/>
-      <c r="P3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P3" s="21"/>
       <c r="Q3" s="22"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
@@ -4007,27 +4001,18 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
       <c r="F6" s="21"/>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="I6" s="22"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
@@ -4036,11 +4021,7 @@
         </is>
       </c>
       <c r="M6" s="22"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
@@ -4049,11 +4030,7 @@
         </is>
       </c>
       <c r="Q6" s="22"/>
-      <c r="R6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R6" s="21"/>
       <c r="S6" s="22"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
@@ -4078,11 +4055,7 @@
         </is>
       </c>
       <c r="E7" s="23"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F7" s="21"/>
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
@@ -4184,7 +4157,7 @@
       <c r="Q8" s="24"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∽</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="S8" s="24"/>
@@ -4229,11 +4202,7 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21"/>
       <c r="Q9" s="22"/>
-      <c r="R9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R9" s="21"/>
       <c r="S9" s="22"/>
       <c r="T9" s="21"/>
       <c r="U9" s="22"/>
@@ -4242,11 +4211,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -4255,11 +4220,7 @@
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -4268,11 +4229,7 @@
         </is>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
@@ -4290,11 +4247,7 @@
         </is>
       </c>
       <c r="S10" s="23"/>
-      <c r="T10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T10" s="21"/>
       <c r="U10" s="23"/>
     </row>
     <row r="11" ht="106.4" customHeight="true">
@@ -4379,7 +4332,7 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∽</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -4431,11 +4384,7 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21"/>
       <c r="G13" s="23"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H13" s="21"/>
       <c r="I13" s="23"/>
       <c r="J13" s="21"/>
       <c r="K13" s="23"/>
@@ -4498,11 +4447,7 @@
         </is>
       </c>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/초혼.xlsx
+++ b/sheets/조재수대금교본/검수/초혼.xlsx
@@ -4157,7 +4157,7 @@
       <c r="Q8" s="24"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太∽</t>
         </is>
       </c>
       <c r="S8" s="24"/>
@@ -4332,7 +4332,7 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太∽</t>
         </is>
       </c>
       <c r="I12" s="22"/>

--- a/sheets/조재수대금교본/검수/초혼.xlsx
+++ b/sheets/조재수대금교본/검수/초혼.xlsx
@@ -3775,32 +3775,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="106.4" customHeight="true">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="106.4" customHeight="true">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="106.4" customHeight="true">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="106.4" customHeight="true">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="106.4" customHeight="true">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="106.4" customHeight="true">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="106.4" customHeight="true">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4207,7 +4207,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="106.4" customHeight="true">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -4250,7 +4250,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="106.4" customHeight="true">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="106.4" customHeight="true">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="106.4" customHeight="true">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="106.4" customHeight="true">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4472,6 +4472,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
 </worksheet>
 </file>